--- a/Kết quả KS Sale.xlsx
+++ b/Kết quả KS Sale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE88D0A6-98BE-4573-9DB5-43E854568EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68515335-A736-4488-A147-4671AB255B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Phòng thuốc 03_2026" sheetId="37" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phòng thuốc 03_2026'!$G$1:$G$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Phòng thuốc 03_2026'!$D$1:$D$177</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3443,7 +3443,7 @@
         <v>204</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="H44" s="24" t="s">
         <v>10</v>
@@ -6571,7 +6571,7 @@
         <v>170</v>
       </c>
       <c r="G136" s="25" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="H136" s="24" t="s">
         <v>3</v>
